--- a/tool/kintone-aggregator/template/アラート検知.xlsx
+++ b/tool/kintone-aggregator/template/アラート検知.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\businessImprovement\tool\提出確認\template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\kintone-aggregator\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADE462D1-6879-43A5-B287-D1884CCE12FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D1B5655-1580-4C22-A275-D6DB6F231A22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{23D1906F-ABF5-443E-AF8C-34868E368ECE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{23D1906F-ABF5-443E-AF8C-34868E368ECE}"/>
   </bookViews>
   <sheets>
     <sheet name="提出状況-当日" sheetId="5" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="研修スケジュール" sheetId="4" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'提出状況-全日'!$C$3:$M$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'提出状況-全日'!$D$3:$N$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'提出状況-当日'!$B$6:$M$7</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="47">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -336,14 +336,17 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>◆全データ</t>
+    <t>アラート</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>◆全日データ</t>
     <rPh sb="1" eb="2">
       <t>ゼン</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>アラート</t>
+    <rPh sb="2" eb="3">
+      <t>ニチ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -640,7 +643,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -839,22 +842,28 @@
     <xf numFmtId="176" fontId="2" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="176" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1204,10 +1213,10 @@
       <c r="B2" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="66" t="s">
+      <c r="C2" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="67"/>
+      <c r="D2" s="71"/>
       <c r="G2" s="54" t="s">
         <v>33</v>
       </c>
@@ -1284,7 +1293,7 @@
       </c>
       <c r="C7" s="49"/>
       <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
+      <c r="E7" s="72"/>
       <c r="F7" s="32"/>
       <c r="G7" s="32"/>
       <c r="H7" s="32"/>
@@ -1305,83 +1314,91 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{870332A5-84D0-46C8-BF43-7ECC8C0CF50C}">
-  <dimension ref="B2:M4"/>
+  <dimension ref="B1:N4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.69921875" customWidth="1"/>
     <col min="2" max="2" width="11.69921875" customWidth="1"/>
-    <col min="3" max="4" width="15.69921875" customWidth="1"/>
-    <col min="5" max="5" width="10.59765625" customWidth="1"/>
-    <col min="6" max="6" width="18.69921875" customWidth="1"/>
-    <col min="7" max="7" width="15.69921875" customWidth="1"/>
-    <col min="8" max="8" width="40.69921875" customWidth="1"/>
-    <col min="9" max="9" width="30.69921875" customWidth="1"/>
-    <col min="10" max="12" width="15.69921875" customWidth="1"/>
-    <col min="13" max="13" width="50.69921875" customWidth="1"/>
+    <col min="3" max="3" width="30.69921875" customWidth="1"/>
+    <col min="4" max="5" width="15.69921875" customWidth="1"/>
+    <col min="6" max="6" width="10.59765625" customWidth="1"/>
+    <col min="7" max="7" width="18.69921875" customWidth="1"/>
+    <col min="8" max="8" width="15.69921875" customWidth="1"/>
+    <col min="9" max="9" width="40.69921875" customWidth="1"/>
+    <col min="10" max="10" width="30.69921875" customWidth="1"/>
+    <col min="11" max="13" width="15.69921875" customWidth="1"/>
+    <col min="14" max="14" width="50.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B2" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D2" s="2"/>
+    <row r="1" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B1" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="C2" s="2"/>
       <c r="E2" s="2"/>
-      <c r="K2" s="45"/>
-      <c r="M2" s="45"/>
-    </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="F2" s="2"/>
+      <c r="L2" s="45"/>
+      <c r="N2" s="45"/>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B3" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="60" t="s">
+      <c r="C3" s="64" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="60" t="s">
         <v>38</v>
       </c>
-      <c r="D3" s="48" t="s">
+      <c r="E3" s="48" t="s">
         <v>38</v>
       </c>
-      <c r="E3" s="43" t="s">
+      <c r="F3" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="43" t="s">
+      <c r="G3" s="43" t="s">
         <v>31</v>
       </c>
-      <c r="G3" s="43" t="s">
+      <c r="H3" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="43" t="s">
+      <c r="I3" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="43" t="s">
+      <c r="J3" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="46" t="s">
+      <c r="K3" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="K3" s="48" t="s">
+      <c r="L3" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="L3" s="47" t="s">
+      <c r="M3" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="M3" s="48" t="s">
+      <c r="N3" s="48" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B4" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="49"/>
+      <c r="C4" s="73"/>
       <c r="D4" s="49"/>
       <c r="E4" s="49"/>
-      <c r="F4" s="32"/>
+      <c r="F4" s="50"/>
       <c r="G4" s="32"/>
       <c r="H4" s="32"/>
       <c r="I4" s="32"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="31"/>
+      <c r="J4" s="32"/>
+      <c r="K4" s="50"/>
       <c r="L4" s="31"/>
       <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -1414,13 +1431,13 @@
       <c r="E2" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="70"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="69"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="67"/>
       <c r="I2" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="71"/>
+      <c r="J2" s="69"/>
     </row>
     <row r="3" spans="2:10" ht="36" x14ac:dyDescent="0.45">
       <c r="B3" s="27" t="s">
@@ -1436,7 +1453,7 @@
         <v>16</v>
       </c>
       <c r="F3" s="29" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G3" s="30" t="s">
         <v>15</v>
@@ -1445,7 +1462,7 @@
         <v>17</v>
       </c>
       <c r="I3" s="63" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J3" s="65" t="s">
         <v>15</v>

--- a/tool/kintone-aggregator/template/アラート検知.xlsx
+++ b/tool/kintone-aggregator/template/アラート検知.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\kintone-aggregator\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D1B5655-1580-4C22-A275-D6DB6F231A22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DEC660D-C9F6-41C9-B4D5-EC29DF21088B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{23D1906F-ABF5-443E-AF8C-34868E368ECE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{23D1906F-ABF5-443E-AF8C-34868E368ECE}"/>
   </bookViews>
   <sheets>
     <sheet name="提出状況-当日" sheetId="5" r:id="rId1"/>
@@ -236,9 +236,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>◆提出状況</t>
-  </si>
-  <si>
     <t>クラス名</t>
   </si>
   <si>
@@ -346,6 +343,13 @@
     </rPh>
     <rPh sb="2" eb="3">
       <t>ニチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>◆当日データ</t>
+    <rPh sb="1" eb="3">
+      <t>トウジツ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -854,17 +858,17 @@
     <xf numFmtId="176" fontId="2" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1206,19 +1210,19 @@
       </c>
       <c r="C1" s="2"/>
       <c r="G1" s="53" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B2" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="70" t="s">
+      <c r="C2" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="71"/>
+      <c r="D2" s="73"/>
       <c r="G2" s="54" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H2" s="55"/>
     </row>
@@ -1229,19 +1233,19 @@
       <c r="C3" s="51"/>
       <c r="D3" s="44"/>
       <c r="G3" s="56" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H3" s="57"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.45">
       <c r="G4" s="58" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H4" s="59"/>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B5" s="2" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -1251,31 +1255,31 @@
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B6" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="60" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="48" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="60" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" s="48" t="s">
-        <v>38</v>
-      </c>
-      <c r="E6" s="43" t="s">
-        <v>37</v>
-      </c>
       <c r="F6" s="43" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G6" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="H6" s="43" t="s">
+      <c r="I6" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="I6" s="43" t="s">
+      <c r="J6" s="46" t="s">
         <v>28</v>
-      </c>
-      <c r="J6" s="46" t="s">
-        <v>29</v>
       </c>
       <c r="K6" s="48" t="s">
         <v>5</v>
@@ -1284,16 +1288,16 @@
         <v>6</v>
       </c>
       <c r="M6" s="48" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B7" s="49" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C7" s="49"/>
       <c r="D7" s="49"/>
-      <c r="E7" s="72"/>
+      <c r="E7" s="70"/>
       <c r="F7" s="32"/>
       <c r="G7" s="32"/>
       <c r="H7" s="32"/>
@@ -1332,7 +1336,7 @@
   <sheetData>
     <row r="1" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B1" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="2:14" x14ac:dyDescent="0.45">
@@ -1350,28 +1354,28 @@
         <v>13</v>
       </c>
       <c r="D3" s="60" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E3" s="48" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F3" s="43" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G3" s="43" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H3" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="43" t="s">
+      <c r="J3" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="43" t="s">
+      <c r="K3" s="46" t="s">
         <v>28</v>
-      </c>
-      <c r="K3" s="46" t="s">
-        <v>29</v>
       </c>
       <c r="L3" s="48" t="s">
         <v>5</v>
@@ -1380,14 +1384,14 @@
         <v>6</v>
       </c>
       <c r="N3" s="48" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B4" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="73"/>
+      <c r="C4" s="71"/>
       <c r="D4" s="49"/>
       <c r="E4" s="49"/>
       <c r="F4" s="50"/>
@@ -1424,7 +1428,7 @@
   <sheetData>
     <row r="1" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B1" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="2:10" x14ac:dyDescent="0.45">
@@ -1447,13 +1451,13 @@
         <v>11</v>
       </c>
       <c r="D3" s="28" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E3" s="29" t="s">
         <v>16</v>
       </c>
       <c r="F3" s="29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G3" s="30" t="s">
         <v>15</v>
@@ -1462,7 +1466,7 @@
         <v>17</v>
       </c>
       <c r="I3" s="63" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J3" s="65" t="s">
         <v>15</v>
@@ -1504,7 +1508,7 @@
   <sheetData>
     <row r="1" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B1" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.45">
@@ -1637,7 +1641,7 @@
   <sheetData>
     <row r="1" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B1" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1659,7 +1663,7 @@
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B1" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.45">
